--- a/HW2/result/HW_2.xlsx
+++ b/HW2/result/HW_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\HW2\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B09636-449D-4F00-BC42-76C9D598A0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B5A3B6-48D9-417B-B2AC-2B095B1333B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{743BE6A8-4582-4DE1-BD9D-D3263963213D}"/>
   </bookViews>
